--- a/data/ams_weekly_data/Audio_Array/business_report_week26.xlsx
+++ b/data/ams_weekly_data/Audio_Array/business_report_week26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W96"/>
+  <dimension ref="A1:W155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,7 +566,11 @@
           <t>B0B4DPX2J2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AM-C1</t>
+        </is>
+      </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
@@ -643,7 +647,11 @@
           <t>B0B4DS678Q</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AM-C4</t>
+        </is>
+      </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
@@ -720,7 +728,11 @@
           <t>B0B4G19R58</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AM-C2</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
@@ -797,7 +809,11 @@
           <t>B0B4G1HPL5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AM-C11</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
@@ -951,7 +967,11 @@
           <t>B0B4G59Y8W</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AM-W13</t>
+        </is>
+      </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
@@ -1028,7 +1048,11 @@
           <t>B0B4G5JG4P</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AM-W14</t>
+        </is>
+      </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
@@ -1182,7 +1206,11 @@
           <t>B0B4G763WS</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AM-W12</t>
+        </is>
+      </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
@@ -1259,7 +1287,11 @@
           <t>B0B4G7VWXD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AA-04</t>
+        </is>
+      </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
@@ -1336,7 +1368,11 @@
           <t>B0B4G8PH2P</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AA-01</t>
+        </is>
+      </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
@@ -1413,7 +1449,11 @@
           <t>B0B4G8ZB64</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AM-C3</t>
+        </is>
+      </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
@@ -1490,7 +1530,11 @@
           <t>B0B4G94VP3</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AA-03</t>
+        </is>
+      </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
@@ -1567,7 +1611,11 @@
           <t>B0B4JRQP22</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AA-02</t>
+        </is>
+      </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
@@ -1644,7 +1692,11 @@
           <t>B0B4K87PR4</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AM-C10</t>
+        </is>
+      </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
@@ -1721,7 +1773,11 @@
           <t>B0B4KC7VBM</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AM-C5</t>
+        </is>
+      </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
@@ -1798,7 +1854,11 @@
           <t>B0BLJVJ2GN</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AA-05</t>
+        </is>
+      </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
@@ -1857,25 +1917,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA76716</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AM-C13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0BLK8DNPD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>B0BLK8DNPD</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AM-C13</t>
+        </is>
+      </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
@@ -1907,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -1919,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>124331.56</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1934,25 +1998,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA76730</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AM-C27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0BLKB6FRR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>B0BLKB6FRR</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AM-C27</t>
+        </is>
+      </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
@@ -1984,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1996,7 +2064,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>410761.49</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2011,25 +2079,29 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FBA76863</t>
+          <t>FBA76742</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AI-03</t>
+          <t>AM-K1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0BLKBJ5HN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>B0BLKBJ5HN</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AM-K1</t>
+        </is>
+      </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
@@ -2061,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -2073,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>13555.92</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2088,25 +2160,29 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FBA77010</t>
+          <t>FBA76720</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AI-04 Black</t>
+          <t>AM-C17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0BPMBMN3S</t>
+          <t>B0BLKCWZQD</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B0BPMBMN3S</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>B0BLKCWZQD</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AM-C17</t>
+        </is>
+      </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
@@ -2165,25 +2241,29 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBA76597</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AA-06</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>B0BPLWW72Y</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AM-C28</t>
+        </is>
+      </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
@@ -2215,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2227,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>6605.08</v>
+        <v>124331.56</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2242,25 +2322,29 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FBA78925</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AM-C11X</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>B0BPLZ5CGV</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI-04 Red</t>
+        </is>
+      </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
@@ -2292,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2304,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>410761.49</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2319,25 +2403,29 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FBA78960</t>
+          <t>FBA76863</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AM-C39</t>
+          <t>AI-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>B0BPM2T7BQ</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI-03</t>
+        </is>
+      </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
@@ -2369,7 +2457,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2381,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>8152.52</v>
+        <v>13555.92</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2396,22 +2484,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA77010</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>AI-04 Black</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0BPMBMN3S</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0BPMBMN3S</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -2446,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2458,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>75022.78</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2473,25 +2561,29 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FBA78974</t>
+          <t>FBA77011</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AA-20</t>
+          <t>AM-C29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0BPMN89NG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>B0BPMN89NG</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AM-C29</t>
+        </is>
+      </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
@@ -2523,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2535,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>8470.33</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2550,25 +2642,29 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FBA78976</t>
+          <t>FBA76597</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AA-22</t>
+          <t>AA-06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>B0BQ7H7418</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AA-06</t>
+        </is>
+      </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
@@ -2600,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2612,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>15673.74</v>
+        <v>6605.08</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -2627,25 +2723,29 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA78203</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AM-C30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>B0C4YTNJG7</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AM-C30</t>
+        </is>
+      </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
@@ -2677,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2689,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>64389.93</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2704,25 +2804,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FBA79009</t>
+          <t>FBA78205</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AM-C32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0C539RBGL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>B0C539RBGL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AM-C32</t>
+        </is>
+      </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
@@ -2754,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2766,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>13550.8</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -2781,25 +2885,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FBA79016</t>
+          <t>FBA78420</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AM-C3a</t>
+          <t>AM-C33</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0C5957W3P</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>B0C5957W3P</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AM-C33</t>
+        </is>
+      </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
@@ -2831,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2843,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>677.12</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -2858,25 +2966,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA78423</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AM-C36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0C598Q6PT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>B0C598Q6PT</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AM-C36</t>
+        </is>
+      </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
@@ -2908,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -2920,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>23295.8</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -2935,25 +3047,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FBA79010</t>
+          <t>FBA78925</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AM-C11X</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>B0CBC7QMNV</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AM-C11X</t>
+        </is>
+      </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
@@ -2985,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -2997,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3981.36</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3012,25 +3128,29 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FBA77171</t>
+          <t>FBA78960</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AC-6XL</t>
+          <t>AM-C39</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>B0CBCB82MT</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AM-C39</t>
+        </is>
+      </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
@@ -3062,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -3074,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>13957.64</v>
+        <v>8152.52</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3089,25 +3209,29 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FBA79064</t>
+          <t>FBA78973</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AA-25</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>B0CF5R3V95</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AA-19</t>
+        </is>
+      </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
@@ -3139,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3151,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>7914.41</v>
+        <v>75022.78</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3166,25 +3290,29 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA78974</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AA-20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>B0CF5RRTDJ</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AA-20</t>
+        </is>
+      </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
@@ -3216,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -3228,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>277573.77</v>
+        <v>8470.33</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3243,25 +3371,29 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FBA79103</t>
+          <t>FBA78976</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AI-10</t>
+          <t>AA-22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>B0CF5SHL15</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AA-22</t>
+        </is>
+      </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
@@ -3293,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3305,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>34141.53</v>
+        <v>15673.74</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3320,25 +3452,29 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FBA79104</t>
+          <t>FBA78975</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AI-11</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>B0CF5TCQKL</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AA-21</t>
+        </is>
+      </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
@@ -3370,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -3382,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>16040.68</v>
+        <v>64389.93</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -3397,25 +3533,29 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA79009</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>B0CH4PMR8K</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AM-C41</t>
+        </is>
+      </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
@@ -3447,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3459,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2371.19</v>
+        <v>13550.8</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -3474,25 +3614,29 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA79016</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AM-C3a</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>B0CH4R1V6S</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AM-C3a</t>
+        </is>
+      </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
@@ -3524,7 +3668,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3536,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>12091.47</v>
+        <v>677.12</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -3551,25 +3695,29 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FBA79106</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AM-C44</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>B0CH4RNWJX</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AM-C43</t>
+        </is>
+      </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
@@ -3601,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3613,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>23295.8</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3628,25 +3776,29 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA79008</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AI-06</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>B0CH4RT4P8</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI-06</t>
+        </is>
+      </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
@@ -3678,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3690,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>4319.5</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -3705,25 +3857,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FBA79379</t>
+          <t>FBA79010</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AM-C45</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>B0CH4T2BJD</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AM-C42</t>
+        </is>
+      </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
@@ -3755,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3767,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>11691.52</v>
+        <v>3981.36</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -3782,25 +3938,29 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FBA79380</t>
+          <t>FBA77171</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AC-6XL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>B0CH4VCD6R</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AC-6XL</t>
+        </is>
+      </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
@@ -3832,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -3844,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>37446.58</v>
+        <v>13957.64</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -3859,25 +4019,29 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FBA79355</t>
+          <t>FBA79064</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AA-19BL</t>
+          <t>AA-25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>B0CJR76Y7G</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AA-25</t>
+        </is>
+      </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
@@ -3909,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -3921,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>8472.879999999999</v>
+        <v>7914.41</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -3936,25 +4100,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FBA79356</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AA-19WL</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>B0CKHVHVQ1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AM-W45</t>
+        </is>
+      </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
@@ -3986,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3998,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>4236.44</v>
+        <v>277573.77</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4013,25 +4181,29 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FBA79448</t>
+          <t>FBA79103</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AM-W35</t>
+          <t>AI-10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>B0CM6NTWBP</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AI-10</t>
+        </is>
+      </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
@@ -4063,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -4075,7 +4247,7 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>34141.53</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4090,25 +4262,29 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FBA79445</t>
+          <t>FBA79104</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>AI-11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>B0CM6NVLT9</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI-11</t>
+        </is>
+      </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
@@ -4140,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -4152,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>6777.96</v>
+        <v>16040.68</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4167,25 +4343,29 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FBA79447</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AM-W34</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>B0CM6WH4ZT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AI-12</t>
+        </is>
+      </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
@@ -4229,7 +4409,7 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>6777.96</v>
+        <v>2371.19</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -4244,25 +4424,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FBA79446</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AM-W33</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>B0CM9HYVDM</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AM-W18</t>
+        </is>
+      </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
@@ -4294,7 +4478,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -4306,7 +4490,7 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>1863.56</v>
+        <v>12091.47</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -4321,25 +4505,29 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FBA79449</t>
+          <t>FBA79106</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AM-W36</t>
+          <t>AM-C44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>B0CM9KJZWQ</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AM-C44</t>
+        </is>
+      </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
@@ -4371,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4383,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>10676.28</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -4398,25 +4586,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FBA79654</t>
+          <t>FBA79108</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AM-C11 Pro</t>
+          <t>AM-W16</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>B0CM9L1QZG</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AM-W16</t>
+        </is>
+      </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
@@ -4448,7 +4640,7 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -4460,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>12440.27</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -4475,25 +4667,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FBA79655</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AM-C44 Pro</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>B0CM9P5CCK</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AM-W17</t>
+        </is>
+      </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
@@ -4525,7 +4721,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4537,7 +4733,7 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>8811.870000000001</v>
+        <v>4319.5</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -4552,25 +4748,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FBA79694</t>
+          <t>FBA79230</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AA-26</t>
+          <t>AM-W46</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>B0CX1XK5R6</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AM-W46</t>
+        </is>
+      </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
@@ -4602,7 +4802,7 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -4614,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>28934.76</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -4629,25 +4829,29 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FBA79482</t>
+          <t>FBA79379</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>AM-C45</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>B0D3LZWTHV</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AM-C45</t>
+        </is>
+      </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
@@ -4679,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4691,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>251850.06</v>
+        <v>11691.52</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -4706,25 +4910,29 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FBA79708</t>
+          <t>FBA79380</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>B0D3M1B4Z8</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AM-C46</t>
+        </is>
+      </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
@@ -4756,7 +4964,7 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -4768,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>29425.39</v>
+        <v>37446.58</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -4783,25 +4991,29 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA79355</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>AA-19BL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>B0D3M86SH1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AA-19BL</t>
+        </is>
+      </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
@@ -4833,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -4845,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>118584.57</v>
+        <v>8472.879999999999</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -4860,25 +5072,29 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FBA79825</t>
+          <t>FBA79356</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GB-02 (AM-C43 + AI-11)</t>
+          <t>AA-19WL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>B0D3Q2T5XX</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AA-19WL</t>
+        </is>
+      </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
@@ -4922,7 +5138,7 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>3261.86</v>
+        <v>4236.44</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -4937,25 +5153,29 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FBA79821</t>
+          <t>FBA79448</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
+          <t>AM-W35</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>B0DFMKY4TT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AM-W35</t>
+        </is>
+      </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
@@ -5014,25 +5234,29 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FBA79824</t>
+          <t>FBA79444</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GB-01 (AM-C43 +AI-10)</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>B0DFMLQBMC</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AM-W20</t>
+        </is>
+      </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
@@ -5064,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -5076,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>4575.42</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -5091,25 +5315,29 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FBA79830</t>
+          <t>FBA79445</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>B0DFMLS8JG</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AM-W32</t>
+        </is>
+      </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
@@ -5141,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -5153,7 +5381,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>8005.92</v>
+        <v>6777.96</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -5168,25 +5396,29 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FBK79009</t>
+          <t>FBA79447</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AM-W34</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>B0DFMLXD9S</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AM-W34</t>
+        </is>
+      </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
@@ -5218,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -5230,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>6777.96</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -5245,25 +5477,29 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FBA79845</t>
+          <t>FBA79446</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>UB-02 (AM-S1 + AA-21)</t>
+          <t>AM-W33</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>B0DFMMTWLY</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AM-W33</t>
+        </is>
+      </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
@@ -5295,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -5307,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>1863.56</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -5322,25 +5558,29 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FBA79846</t>
+          <t>FBA79449</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AM-C11X Pro</t>
+          <t>AM-W36</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
+          <t>B0DFMNGFTD</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AM-W36</t>
+        </is>
+      </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
@@ -5372,7 +5612,7 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -5384,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>10676.28</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -5399,25 +5639,29 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA79465</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0DFMQCGT1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
+          <t>B0DFMQCGT1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AM-W21</t>
+        </is>
+      </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
@@ -5476,25 +5720,29 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FBA79841</t>
+          <t>FBA79653</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AH-60-BL</t>
+          <t>AM-C45 Pro</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+          <t>B0DN6LJZBR</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AM-C45 Pro</t>
+        </is>
+      </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
@@ -5526,7 +5774,7 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -5538,7 +5786,7 @@
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>18634.73</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -5553,25 +5801,29 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA79654</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AH-60-RD</t>
+          <t>AM-C11 Pro</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
+          <t>B0DN6MNS1X</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AM-C11 Pro</t>
+        </is>
+      </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
@@ -5603,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -5615,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>3388.14</v>
+        <v>12440.27</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -5630,25 +5882,29 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA79655</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AM-C44 Pro</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>B0DN6PFWNK</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AM-C44 Pro</t>
+        </is>
+      </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
@@ -5680,7 +5936,7 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -5692,7 +5948,7 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>14267.79</v>
+        <v>8811.870000000001</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -5707,25 +5963,29 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA79694</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
+          <t>B0DT6T6N6B</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AA-26</t>
+        </is>
+      </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
@@ -5757,7 +6017,7 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -5769,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>66398.92</v>
+        <v>28934.76</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -5784,25 +6044,29 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FBA79820</t>
+          <t>FBA79482</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AC-3XL</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
+          <t>B0DXFPM4N2</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AM-S1</t>
+        </is>
+      </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
@@ -5834,7 +6098,7 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -5846,7 +6110,7 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>1522.01</v>
+        <v>251850.06</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -5861,25 +6125,29 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FBA79904</t>
+          <t>FBA79722</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0F2HYY7JF</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>B0F2HYY7JF</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AM-W21</t>
+        </is>
+      </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
@@ -5911,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -5923,7 +6191,7 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>59316.11</v>
+        <v>0</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -5938,25 +6206,29 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FBA79905</t>
+          <t>FBA79783</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+          <t>B0FF9R3GKK</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AM-C47</t>
+        </is>
+      </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
@@ -5988,7 +6260,7 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -6000,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>3942.37</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -6015,25 +6287,29 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FBA79908</t>
+          <t>FBA79708</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+          <t>B0FFB6YJM1</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>SB-01</t>
+        </is>
+      </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
@@ -6065,7 +6341,7 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -6077,7 +6353,7 @@
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>4066.95</v>
+        <v>29425.39</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -6092,25 +6368,29 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FBA79906</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>B0FG88HVQ8</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AH-50</t>
+        </is>
+      </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
@@ -6142,7 +6422,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -6154,7 +6434,7 @@
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>10083.9</v>
+        <v>118584.57</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -6169,25 +6449,29 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA79825</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AM-W47 Wired</t>
+          <t>GB-02 (AM-C43 + AI-11)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t>B0FJ2DT13L</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>GB-02 (AM-C43 + AI-11)</t>
+        </is>
+      </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
@@ -6219,7 +6503,7 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -6231,7 +6515,7 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>21338.1</v>
+        <v>3261.86</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -6246,25 +6530,29 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA79823</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AM-W47 Wireless</t>
+          <t>PB-01 (AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
+          <t>B0FJ2HZCVN</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PB-01 (AM-C11 + AI-04)</t>
+        </is>
+      </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
@@ -6296,7 +6584,7 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -6308,7 +6596,7 @@
         <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>4827.96</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -6323,25 +6611,29 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FBA79969</t>
+          <t>FBA79822</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>UB-03 (AM-S1 + AA-22)</t>
+          <t>KB-01 (AM-W32 + AI-12)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
+          <t>B0FJ2J6MTF</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>KB-01 (AM-W32 + AI-12)</t>
+        </is>
+      </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
@@ -6400,25 +6692,29 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FBA79957</t>
+          <t>FBA79821</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AM-W23</t>
+          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>B0FJ2JJZL3</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
+        </is>
+      </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
@@ -6450,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -6462,7 +6758,7 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>2456.78</v>
+        <v>0</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -6477,25 +6773,29 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FBA79958</t>
+          <t>FBA79824</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AM-W24</t>
+          <t>GB-01 (AM-C43 +AI-10)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>B0FJ2K95XT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>GB-01 (AM-C43 +AI-10)</t>
+        </is>
+      </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
@@ -6527,7 +6827,7 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -6539,7 +6839,7 @@
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>2769.16</v>
+        <v>4575.42</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -6554,25 +6854,29 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FBA79842</t>
+          <t>FBA79826</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>B0FJ2LQT7K</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
+        </is>
+      </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
@@ -6604,7 +6908,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -6616,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>22366.08</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -6631,25 +6935,29 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FBA79961</t>
+          <t>FBA79833</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>B0FJ8PZ9H7</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
+        </is>
+      </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
@@ -6681,7 +6989,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -6693,7 +7001,7 @@
         <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>106317.74</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -6708,25 +7016,29 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA79832</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>GB-05 (AM-C43 + AI-06)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+          <t>B0FJ8S53GW</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>GB-05 (AM-C43 + AI-06)</t>
+        </is>
+      </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
@@ -6758,7 +7070,7 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -6770,7 +7082,7 @@
         <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>35589.84</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -6785,25 +7097,29 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FBA79964</t>
+          <t>FBA79827</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AM-Pro12</t>
+          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>B0FJ8S5XJ8</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
+        </is>
+      </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
@@ -6835,7 +7151,7 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -6847,7 +7163,7 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>19490.68</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -6862,25 +7178,29 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FBA79968</t>
+          <t>FBA79834</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0FJ8T4WXM</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>B0FJ8T4WXM</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
+        </is>
+      </c>
       <c r="F84" t="n">
         <v>0</v>
       </c>
@@ -6912,7 +7232,7 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -6924,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>66091.52</v>
+        <v>0</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -6939,25 +7259,29 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA79830</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>GB-03 (AI-12 + AM-C43)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>B0FJ8TSQK1</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>GB-03 (AI-12 + AM-C43)</t>
+        </is>
+      </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
@@ -6989,7 +7313,7 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -7001,7 +7325,7 @@
         <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>64314.39</v>
+        <v>8005.92</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -7016,25 +7340,29 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FBA80016</t>
+          <t>FBA79835</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0FJ8TWCQZ</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>B0FJ8TWCQZ</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
+        </is>
+      </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
@@ -7066,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -7078,7 +7406,7 @@
         <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>2795.76</v>
+        <v>0</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -7093,25 +7421,29 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FBA80007</t>
+          <t>FBA79831</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MT-12</t>
+          <t>GB-04 (AM-C45 + AI-06)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0FJ8W5Y9Q</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
+          <t>B0FJ8W5Y9Q</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>GB-04 (AM-C45 + AI-06)</t>
+        </is>
+      </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
@@ -7143,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -7155,7 +7487,7 @@
         <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>30505.09</v>
+        <v>0</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -7170,25 +7502,29 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FBA79981</t>
+          <t>FBA79836</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AK-61 Neo</t>
+          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0FJ8Z1W81</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>B0FJ8Z1W81</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
+        </is>
+      </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
@@ -7220,7 +7556,7 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -7232,7 +7568,7 @@
         <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>12709.32</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -7247,25 +7583,29 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FBA79980</t>
+          <t>FBM79783</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AK-37-W</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0FJS57732</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
+          <t>B0FJS57732</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AM-C47</t>
+        </is>
+      </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
@@ -7297,7 +7637,7 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -7309,7 +7649,7 @@
         <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>6777.96</v>
+        <v>0</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -7324,25 +7664,29 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FBA79982</t>
+          <t>FBK79708</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AK-61 Pro</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0FJS7JZ4V</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
+          <t>B0FJS7JZ4V</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>SB-01</t>
+        </is>
+      </c>
       <c r="F90" t="n">
         <v>0</v>
       </c>
@@ -7374,7 +7718,7 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -7386,7 +7730,7 @@
         <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>13980.5</v>
+        <v>0</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -7401,25 +7745,29 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FBA79979</t>
+          <t>FBK79009</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AK-37-B</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
+          <t>B0FLYHJ6DK</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AM-C41</t>
+        </is>
+      </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
@@ -7451,7 +7799,7 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -7463,7 +7811,7 @@
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>3388.98</v>
+        <v>0</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -7478,25 +7826,29 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBK79010</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
+          <t>B0FLYJFC22</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AM-C42</t>
+        </is>
+      </c>
       <c r="F92" t="n">
         <v>0</v>
       </c>
@@ -7528,7 +7880,7 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -7540,7 +7892,7 @@
         <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>202261.98</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -7555,25 +7907,29 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FBA79996</t>
+          <t>FBA79845</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AM-C49</t>
+          <t>UB-02 (AM-S1 + AA-21)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
+          <t>B0FN7B3KWS</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>UB-02 (AM-S1 + AA-21)</t>
+        </is>
+      </c>
       <c r="F93" t="n">
         <v>0</v>
       </c>
@@ -7632,25 +7988,29 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FBA80002</t>
+          <t>FBA79846</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AM-W33 Pro</t>
+          <t>AM-C11X Pro</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
+          <t>B0FN7C25VS</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AM-C11X Pro</t>
+        </is>
+      </c>
       <c r="F94" t="n">
         <v>0</v>
       </c>
@@ -7682,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -7694,7 +8054,7 @@
         <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>2880.51</v>
+        <v>0</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -7709,25 +8069,29 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA79847</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
+          <t>B0FN7FYZM3</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
+        </is>
+      </c>
       <c r="F95" t="n">
         <v>0</v>
       </c>
@@ -7759,7 +8123,7 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -7771,7 +8135,7 @@
         <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>3287.28</v>
+        <v>0</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -7786,77 +8150,4856 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>FBA79815</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>AM-W19</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>B0FPR7VFCH</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>B0FPR7VFCH</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AM-W19</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>FBA79816</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>AM-W22</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>B0FPR962YS</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>B0FPR962YS</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AM-W22</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>FBA79841</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>AH-60-BL</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>B0FQBTRM28</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>B0FQBTRM28</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AH-60-BL</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>18634.73</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>FBA79840</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>AH-60-RD</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>B0FQBWV1ST</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>B0FQBWV1ST</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AH-60-RD</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>3388.14</v>
+      </c>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>FBA79838</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>AH-40 SL</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>B0FQBX8J17</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>B0FQBX8J17</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AH-40 SL</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>14267.79</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FBA79839</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>AH-45 BK</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>B0FQBXS6Y2</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>B0FQBXS6Y2</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AH-45 BK</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>66398.92</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>FBA79820</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>AC-3XL</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>B0FQJWWDVK</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>B0FQJWWDVK</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AC-3XL</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>1522.01</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>FBA79904</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>B0FTVQQVDC</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>B0FTVQQVDC</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>59316.11</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>FBA79905</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>B0FTVSH458</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>B0FTVSH458</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>3942.37</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>FBA79908</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>B0FTVV1QJY</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>B0FTVV1QJY</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>4066.95</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>FBA79906</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>B0FTVVLNS9</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>B0FTVVLNS9</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>10083.9</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>FBA79909</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>AM-W20</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>B0FVM17Q4W</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>B0FVM17Q4W</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AM-W20</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>FBA79967</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>AM-W19</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>B0G2C2RCXN</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>B0G2C2RCXN</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AM-W19</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>FBA79959</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>AM-W47 Wired</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>B0G39ZHDYP</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>B0G39ZHDYP</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AM-W47 Wired</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>21338.1</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>FBA79960</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>AM-W47 Wireless</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>B0G3B152FR</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>B0G3B152FR</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AM-W47 Wireless</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>4827.96</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>FBA79969</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>UB-03 (AM-S1 + AA-22)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>B0G3B677Z5</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>B0G3B677Z5</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>UB-03 (AM-S1 + AA-22)</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>FBA79957</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>AM-W23</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>B0G3Q517Y2</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>B0G3Q517Y2</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AM-W23</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>2456.78</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>FBA79958</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>AM-W24</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>B0G3Q59X8C</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>B0G3Q59X8C</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AM-W24</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>2769.16</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>FBA79842</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>AM-C48</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>B0G4DNF8RZ</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>B0G4DNF8RZ</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AM-C48</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" t="n">
+        <v>22366.08</v>
+      </c>
+      <c r="U114" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>FBA79963</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>AM-Pro8</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>B0G53CB72D</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>B0G53CB72D</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AM-Pro8</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>FBA79961</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>AI-13</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>B0G53H49BS</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>B0G53H49BS</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AI-13</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>106317.74</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>FBA79966</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>AM-Mix10</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>B0G53KWRVW</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>B0G53KWRVW</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AM-Mix10</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" t="n">
+        <v>35589.84</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>FBA79964</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>AM-Pro12</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>B0G53KWRWH</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>B0G53KWRWH</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>19490.68</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>FBA79968</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>AI-14</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>B0G53M9258</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>B0G53M9258</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AI-14</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>66091.52</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>FBA79965</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>AM-Mix6</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>B0G53PRM34</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>B0G53PRM34</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AM-Mix6</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>FBA79972</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>B0GCP1J2HC</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>B0GCP1J2HC</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>64314.39</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>FBA79974</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>AM-S1</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>B0GD8JSPB1</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>B0GD8JSPB1</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AM-S1</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>FBA80016</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>AM-W22</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>B0GKPXQ8G3</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>B0GKPXQ8G3</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AM-W22</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>2795.76</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>FBA79956</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>A3-XLR</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>B0GMPGNXX3</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>B0GMPGNXX3</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>A3-XLR</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>FBA80007</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>MT-12</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>B0GN2LHJY4</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>B0GN2LHJY4</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>MT-12</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>30505.09</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>FBA79981</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>AK-61 Neo</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>B0GN8MFDGZ</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>B0GN8MFDGZ</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AK-61 Neo</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>12709.32</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>FBA79980</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>AK-37-W</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>B0GN8MMKY1</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>B0GN8MMKY1</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AK-37-W</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>6777.96</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>FBA79982</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>AK-61 Pro</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>B0GN8MPYPG</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>B0GN8MPYPG</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AK-61 Pro</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>13980.5</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>FBA79979</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>AK-37-B</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>B0GN8RQJRG</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>B0GN8RQJRG</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AK-37-B</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>3388.98</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>FBA79848</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>AM-S2</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AM-S2</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>202261.98</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>FBA79814</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>AH-50 Ear Cushion</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>B0GNM35G8X</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>B0GNM35G8X</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AH-50 Ear Cushion</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>FBA80009</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>AM-C51</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>B0GW8R2RYM</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>B0GW8R2RYM</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AM-C51</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>FBA79995</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>AM-C50</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>B0GW8VBCBL</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>B0GW8VBCBL</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AM-C50</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>FBA80000</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>DP-718H</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>B0GW8XGPB2</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>B0GW8XGPB2</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>DP-718H</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>FBA79998</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>B0GW8YC59C</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>B0GW8YC59C</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>FBA79996</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>AM-C49</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>B0GW8Z556N</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>B0GW8Z556N</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AM-C49</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>FBA80010</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>AM-C52</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>B0GW8ZQRFK</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>B0GW8ZQRFK</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AM-C52</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>FBA80004</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>AM-W36 Pro</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>B0GW92316G</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>B0GW92316G</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AM-W36 Pro</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>FBA80001</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>USB718</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>B0GW92TQGV</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>B0GW92TQGV</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>USB718</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>FBA80003</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>AM-W32 Pro</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>B0GW92TTMS</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>B0GW92TTMS</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AM-W32 Pro</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>FBA79999</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>JTG800</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>B0GW92TVVC</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>B0GW92TVVC</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>JTG800</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>FBA80005</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>T-835</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>B0GW96CQMG</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>B0GW96CQMG</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>T-835</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>FBA80002</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>AM-W33 Pro</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>B0GW96SHSK</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>B0GW96SHSK</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AM-W33 Pro</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>2880.51</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>FBA79975</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>AE831</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>B0GXP7LJ75</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>B0GXP7LJ75</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AE831</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>FBA80084</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BE-4</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>B0GXP97CZG</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>B0GXP97CZG</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>BE-4</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
+        <v>3287.28</v>
+      </c>
+      <c r="U145" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
           <t>FBA80085</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>M6</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>B0GXPBHDRF</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>B0GXPBHDRF</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="n">
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
         <v>4</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="n">
+      <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
         <v>23725.44</v>
       </c>
-      <c r="U96" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" t="n">
+      <c r="U146" t="n">
+        <v>0</v>
+      </c>
+      <c r="V146" t="n">
+        <v>0</v>
+      </c>
+      <c r="W146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>FBA80075</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PB-16 (AH-50+AI-13+AM-C2)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>B0GXPGBQB1</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>B0GXPGBQB1</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>PB-16 (AH-50+AI-13+AM-C2)</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" t="n">
+        <v>0</v>
+      </c>
+      <c r="V147" t="n">
+        <v>0</v>
+      </c>
+      <c r="W147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>FBA80104</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>UB-04 (AM-S2+AA-21+AI-04+AM-C2)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>B0GXY7YJWP</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>B0GXY7YJWP</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>UB-04 (AM-S2+AA-21+AI-04+AM-C2)</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>FBA80074</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>PB-15 (AH-50+AM-C2+AI-04)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>B0GY827J9C</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>B0GY827J9C</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>PB-15 (AH-50+AM-C2+AI-04)</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="n">
+        <v>0</v>
+      </c>
+      <c r="V149" t="n">
+        <v>0</v>
+      </c>
+      <c r="W149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>FBA80076</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PB-17 (AH-40-SL+AM-C43+AI-13)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>B0GY857139</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>B0GY857139</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>PB-17 (AH-40-SL+AM-C43+AI-13)</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>FBA80143</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>AM-S2</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>B0H1MTP2ZP</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>B0H1MTP2ZP</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AM-S2</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="n">
+        <v>0</v>
+      </c>
+      <c r="V151" t="n">
+        <v>0</v>
+      </c>
+      <c r="W151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>FBA80106</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>UB-06 (AM-S2+AA-22)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>B0H2FCK54H</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>B0H2FCK54H</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>UB-06 (AM-S2+AA-22)</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="n">
+        <v>0</v>
+      </c>
+      <c r="T152" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" t="n">
+        <v>0</v>
+      </c>
+      <c r="V152" t="n">
+        <v>0</v>
+      </c>
+      <c r="W152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>FBA80110</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>X5</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>B0H2Z6R6V8</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>B0H2Z6R6V8</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>X5</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>FBA80109</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>B0H2ZCQFTZ</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>B0H2ZCQFTZ</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" t="n">
+        <v>0</v>
+      </c>
+      <c r="W154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>FBA80142</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>AM-C5 White</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>B0H3LHF2WW</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>B0H3LHF2WW</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AM-C5 White</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="n">
+        <v>0</v>
+      </c>
+      <c r="V155" t="n">
+        <v>0</v>
+      </c>
+      <c r="W155" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/ams_weekly_data/Audio_Array/business_report_week26.xlsx
+++ b/data/ams_weekly_data/Audio_Array/business_report_week26.xlsx
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>12135</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>16981</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -614,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>511757.94</v>
+        <v>514062.18</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -665,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -776,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>19316.95</v>
+        <v>22439.86</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1066,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>10676.28</v>
+        <v>16014.42</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1335,7 +1335,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>17278.02</v>
+        <v>20157.68</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1404,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>7284.74</v>
+        <v>9105.93</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3383.04</v>
+        <v>3810.16</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2236</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2530</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>16942.4</v>
+        <v>19060.2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>812</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1070</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>16433.88</v>
+        <v>18509.3</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1142</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>15950</v>
+        <v>16505.93</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>845</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1109</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>124331.56</v>
+        <v>144014.61</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>11068</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>15304</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2376,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2388,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>410761.49</v>
+        <v>423121.18</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>928</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1173</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>13555.92</v>
+        <v>16859.67</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2678,7 +2678,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2708,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>6605.08</v>
+        <v>9907.619999999999</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2840,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3083,7 +3083,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>822</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>8152.52</v>
+        <v>10822.04</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -3245,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1124</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3263,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3275,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>75022.78</v>
+        <v>81546.50999999999</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>664</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -3407,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>15673.74</v>
+        <v>18893.23</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1284</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1741</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>13550.8</v>
+        <v>20122.96</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -3650,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>909</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1294</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3893,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>514</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -3974,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>783</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -3992,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>13957.64</v>
+        <v>14898.32</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>2444</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -4136,7 +4136,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>3341</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -4154,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>277573.77</v>
+        <v>286555.13</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1487</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -4217,7 +4217,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>2286</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -4247,7 +4247,7 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>34141.53</v>
+        <v>36794.07</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1354</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1993</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>964</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -4397,7 +4397,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -4409,7 +4409,7 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2371.19</v>
+        <v>3556.78</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -4541,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>458</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -4622,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1370</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1632</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>858</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -5045,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -5057,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>8472.879999999999</v>
+        <v>12709.32</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -5108,7 +5108,7 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>366</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -5189,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -5219,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>3050</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -5351,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -5432,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -5513,7 +5513,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -5594,7 +5594,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -5675,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -5756,7 +5756,7 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -5837,7 +5837,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1048</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -5999,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1538</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>28934.76</v>
+        <v>32523.74</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -6068,7 +6068,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>4663</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -6080,7 +6080,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>6572</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -6242,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>2754</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -6323,7 +6323,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -6341,7 +6341,7 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -6353,7 +6353,7 @@
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>29425.39</v>
+        <v>32600.81</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>2514</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -6404,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>3646</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -6422,7 +6422,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>118584.57</v>
+        <v>122006.6</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -6485,7 +6485,7 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -6503,7 +6503,7 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -6515,7 +6515,7 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>3261.86</v>
+        <v>6523.72</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>845</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>988</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -6809,7 +6809,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -6890,7 +6890,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -6971,7 +6971,7 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -6989,7 +6989,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -7001,7 +7001,7 @@
         <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>23388.14</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -7040,7 +7040,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -7052,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -7214,7 +7214,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -7295,7 +7295,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -7538,7 +7538,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -7718,7 +7718,7 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -7730,7 +7730,7 @@
         <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>3048.31</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -7781,7 +7781,7 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -7799,7 +7799,7 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -7811,7 +7811,7 @@
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>1355.08</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -7862,7 +7862,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -7892,7 +7892,7 @@
         <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>1990.68</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1201</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -7943,7 +7943,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>1438</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -7961,7 +7961,7 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -7973,7 +7973,7 @@
         <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>11016.1</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -8024,7 +8024,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -8186,7 +8186,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>322</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -8285,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -8297,7 +8297,7 @@
         <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>2795.76</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -8336,7 +8336,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -8348,7 +8348,7 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>371</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>417</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -8498,7 +8498,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -8510,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -8528,7 +8528,7 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -8540,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>14267.79</v>
+        <v>15453.38</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -8579,7 +8579,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -8609,7 +8609,7 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -8621,7 +8621,7 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>66398.92</v>
+        <v>73242.14</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -8672,7 +8672,7 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -8702,7 +8702,7 @@
         <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>1522.01</v>
+        <v>1902.52</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -8741,7 +8741,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -8753,7 +8753,7 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>1430</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -8915,7 +8915,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>4066.95</v>
+        <v>20334.75</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -8996,7 +8996,7 @@
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -9014,7 +9014,7 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -9026,7 +9026,7 @@
         <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>10083.9</v>
+        <v>20167.8</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -9077,7 +9077,7 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -9095,7 +9095,7 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -9107,7 +9107,7 @@
         <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>3388.14</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -9158,7 +9158,7 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -9227,7 +9227,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>1061</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -9239,7 +9239,7 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
+        <v>1560</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -9257,7 +9257,7 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>21338.1</v>
+        <v>24386.41</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -9308,7 +9308,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -9320,7 +9320,7 @@
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -9338,7 +9338,7 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
         <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>4827.96</v>
+        <v>16093.21</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>674</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -9401,7 +9401,7 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>745</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -9470,7 +9470,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -9551,7 +9551,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -9563,7 +9563,7 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -9632,7 +9632,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>565</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -9662,7 +9662,7 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -9674,7 +9674,7 @@
         <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>22366.08</v>
+        <v>25161.84</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -9725,7 +9725,7 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>6356</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -9806,7 +9806,7 @@
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>8767</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -9824,7 +9824,7 @@
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -9836,7 +9836,7 @@
         <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>106317.74</v>
+        <v>108689.77</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>1195</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -9887,7 +9887,7 @@
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>1715</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -9917,7 +9917,7 @@
         <v>0</v>
       </c>
       <c r="T117" t="n">
-        <v>35589.84</v>
+        <v>53384.75999999999</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -10033,7 +10033,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>4273</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -10045,7 +10045,7 @@
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>5691</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -10063,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -10075,7 +10075,7 @@
         <v>0</v>
       </c>
       <c r="T119" t="n">
-        <v>66091.52</v>
+        <v>77106.77</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -10114,7 +10114,7 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -10126,7 +10126,7 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>1170</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -10207,7 +10207,7 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>1573</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -10225,7 +10225,7 @@
         <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -10237,7 +10237,7 @@
         <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>64314.39</v>
+        <v>71516.92999999999</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -10288,7 +10288,7 @@
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -10369,7 +10369,7 @@
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -10438,7 +10438,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -10468,7 +10468,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -10480,7 +10480,7 @@
         <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>0</v>
+        <v>507.63</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>687</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>935</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -10549,7 +10549,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
@@ -10561,7 +10561,7 @@
         <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>30505.09</v>
+        <v>38131.36</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -10600,7 +10600,7 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>646</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -10612,7 +10612,7 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>962</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -10630,7 +10630,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
@@ -10642,7 +10642,7 @@
         <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>12709.32</v>
+        <v>16945.76</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -10693,7 +10693,7 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>395</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -10762,7 +10762,7 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>548</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -10774,7 +10774,7 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>739</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -10843,7 +10843,7 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -10855,7 +10855,7 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -10873,7 +10873,7 @@
         <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q129" t="n">
         <v>0</v>
@@ -10885,7 +10885,7 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>3388.98</v>
+        <v>10166.95</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>10028</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -10936,7 +10936,7 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>13071</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q130" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>202261.98</v>
+        <v>215311.13</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -11017,7 +11017,7 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -11035,7 +11035,7 @@
         <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q131" t="n">
         <v>0</v>
@@ -11047,7 +11047,7 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>0</v>
+        <v>465.25</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -11086,7 +11086,7 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -11098,7 +11098,7 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -11167,7 +11167,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -11179,7 +11179,7 @@
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -11260,7 +11260,7 @@
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -11341,7 +11341,7 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -11410,7 +11410,7 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -11422,7 +11422,7 @@
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -11491,7 +11491,7 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -11503,7 +11503,7 @@
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -11665,7 +11665,7 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -11746,7 +11746,7 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -11827,7 +11827,7 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -11845,7 +11845,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
@@ -11857,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>4236.44</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -11896,7 +11896,7 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -11908,7 +11908,7 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -11977,7 +11977,7 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -11989,7 +11989,7 @@
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -12058,7 +12058,7 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -12070,7 +12070,7 @@
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -12151,7 +12151,7 @@
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>911</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -12169,7 +12169,7 @@
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q145" t="n">
         <v>0</v>
@@ -12181,7 +12181,7 @@
         <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>3287.28</v>
+        <v>12945.75</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>2167</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -12232,7 +12232,7 @@
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>2895</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -12250,7 +12250,7 @@
         <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q146" t="n">
         <v>0</v>
@@ -12262,7 +12262,7 @@
         <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>23725.44</v>
+        <v>29656.8</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -12301,7 +12301,7 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -12313,7 +12313,7 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
@@ -12382,7 +12382,7 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -12394,7 +12394,7 @@
         <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
+        <v>705</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -12475,7 +12475,7 @@
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
@@ -12544,7 +12544,7 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -12556,7 +12556,7 @@
         <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
@@ -12625,7 +12625,7 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -12637,7 +12637,7 @@
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
@@ -12706,7 +12706,7 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -12718,7 +12718,7 @@
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="K152" t="n">
         <v>0</v>
@@ -12787,7 +12787,7 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -12799,7 +12799,7 @@
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
@@ -12898,7 +12898,7 @@
         <v>0</v>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q154" t="n">
         <v>0</v>
@@ -12910,7 +12910,7 @@
         <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>0</v>
+        <v>15253.39</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -12949,7 +12949,7 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -12961,7 +12961,7 @@
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="K155" t="n">
         <v>0</v>
